--- a/data/trans_camb/IP1019-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1019-Clase-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>-1,88; 0,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>-1,68; 0,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,0</t>
+          <t>-4,82; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,0</t>
+          <t>-5,79; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-2,45; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,14 +1567,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>-0,57; 0,0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>-0,56; 0,0</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-0,56; 0,0</t>
-        </is>
-      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>-0,49; 0,0</t>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,0</t>
+          <t>-0,35; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,0</t>
+          <t>-0,32; 0,0</t>
         </is>
       </c>
     </row>
